--- a/Teacher Toolkit/Scheme of Work - Homework and Consolidation.xlsx
+++ b/Teacher Toolkit/Scheme of Work - Homework and Consolidation.xlsx
@@ -500,17 +500,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Induction &amp; Diagnostic</t>
+          <t>Induction &amp; diagnostic; VS Code/Python setup</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Complete the diagnostic task (knowledge + research/programming); set up VS Code + Python + Google Classroom.</t>
+          <t>Complete the diagnostic task; verify VS Code + Python + Classroom access.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Read subject booklet; build notes &amp; folder structure (VESPA Systems); skim course overview.</t>
+          <t>Read subject booklet; set up notes/folders (VESPA Systems); skim 00 START HERE.</t>
         </is>
       </c>
     </row>
@@ -527,17 +527,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1.1.1 Processor structure &amp; function</t>
+          <t>1.1.1 CPU, FDE, performance, Von Neumann/Harvard</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.1.1 (closed-book, self-mark) + register/FDE sections of Worksheet 1.1. Programming: Workbook 1 sequence/selection/iteration.</t>
+          <t>Homework 1.1.1 (/20). Programming: Workbook 1 s1-2.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Make &amp; learn Flashcards 1.1; cover-and-recall KO 1.1; redo missed diagnostic questions.</t>
+          <t>Revision Notes 1.1.1 cover-and-recall; start Flashcards 1.1; redo missed diagnostic Qs.</t>
         </is>
       </c>
     </row>
@@ -554,17 +554,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1.1.2 Types of processor (KA1)</t>
+          <t>1.1.2 Pipelining, CISC/RISC, GPUs, multicore (KA1)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Revise for KA1 with KO 1.1 + Flashcards 1.1; then Quiz 1.1.2.</t>
+          <t>Homework 1.1.2 (/20); revise for KA1 with Knowledge Organiser 1.1.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Interleave: re-do Quiz 1.1.1 Section A closed-book. Programming: Workbook 1 strings/lists.</t>
+          <t>Worksheet (quiz) 1.1.1 closed-book, self-mark; Flashcards 1.1.</t>
         </is>
       </c>
     </row>
@@ -581,17 +581,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1.1.3 Input/output &amp; storage; 2.1.1 Thinking abstractly</t>
+          <t>1.1.3 I/O &amp; storage; RAM/ROM; 2.1.1 Thinking abstractly (KA1 fb)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.1.3 + Quiz 2.1.1; act on KA1 feedback (redo 2 weakest).</t>
+          <t>Homework 1.1.3 + Homework 2.1.1; act on KA1 feedback (error log).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Retrieval of 1.1.1-1.1.2 via shuffled Flashcards 1.1. Programming: Workbook 1 operators.</t>
+          <t>Quizzes 1.1.2 &amp; 2.1.1; Revision Notes 1.1.3.</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1.2.1 Systems software; 2.1.2 Thinking ahead (CAP1/KA2)</t>
+          <t>1.2.1 OS, scheduling, interrupts; 2.1.2 Thinking ahead (CAP1/KA2)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.2.1 (A-B); start Quiz 2.1.2; prepare for CAP1/KA2.</t>
+          <t>Homework 1.2.1; prep CAP1/KA2 with Organiser 1.1 + Flashcards.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Spaced retrieval of 1.1: Mini-paper 1.1 Section A, timed. Programming: Workbook 1 selection.</t>
+          <t>Quiz 1.1.3; Mini-Paper 1.1 Section A timed (first spaced retrieval of 1.1).</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Review wk1; 1.2.1 (BIOS, drivers, VMs)</t>
+          <t>Review wk 1; 1.2.1 BIOS, drivers, VMs (CAP1/KA2 fb)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Finish Quiz 1.2.1; act on CAP1/KA2 feedback (error log).</t>
+          <t>Homework 2.1.2; act on CAP1/KA2 feedback.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>File-check prep (Systems). Mixed Flashcards 1.1+1.2. Programming: Workbook 1 iteration.</t>
+          <t>File-check prep; Quiz 1.2.1; mixed Flashcards 1.1+1.2.</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1.2.2 Applications generation; 2.1.2 Thinking ahead (KA3; CAP1 due)</t>
+          <t>1.2.2 Translators &amp; compilers; 2.1.2 caching/reuse (KA3; CAP1 due 12 Oct)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.2.2 + complete Quiz 2.1.2; stages-of-compilation drill (Worksheet 1.2).</t>
+          <t>Homework 1.2.2 (/20); compilation-stages drill (End-of-Topic Worksheet 1.2 sA).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Cumulative before half term: full Mini-paper 1.1, timed &amp; marked. Programming: Workbook 1 nested.</t>
+          <t>Full Mini-Paper 1.1, timed &amp; marked; Quiz 2.1.2.</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Optional: finish outstanding quiz.</t>
+          <t>Finish any outstanding sheet.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>10 min/day Flashcards 1.1-1.2. Light, spaced.</t>
+          <t>10 min/day Flashcards 1.1-1.2 - light and spaced.</t>
         </is>
       </c>
     </row>
@@ -716,17 +716,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1.2.3 Software methodologies; 2.1.3 Thinking procedurally</t>
+          <t>1.2.3 Methodologies, test strategies; 2.1.3 Thinking procedurally (KA3 fb)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.2.3 + methodology-match (Worksheet 1.2); Quiz 2.1.3.</t>
+          <t>Homework 1.2.3 + Homework 2.1.3.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Spaced retrieval 1.1 + 1.2.1/1.2.2 (mixed). Programming: Workbook 1 string manipulation.</t>
+          <t>Quiz 1.2.2; Revision Notes 1.2.3; act on KA3 feedback.</t>
         </is>
       </c>
     </row>
@@ -743,17 +743,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 Types of programming language (CAP2/KA4)</t>
+          <t>1.2.4 Paradigms, assembly, OOP (CAP2/KA4)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.2.4 (addressing-mode calc); LMC practice; revise CAP2/KA4 with KO 1.2.</t>
+          <t>Homework 1.2.4 (/20); prep CAP2/KA4 with Organiser 1.2.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Retrieval: Mini-paper 1.1 + Flashcards 1.2.1-1.2.3. Programming: Workbook 1 arrays.</t>
+          <t>Quiz 1.2.3; Flashcards 1.2; Mini-Paper 1.1 re-run of wrong Qs.</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1.3.1 Compression/encryption; 1.3.2 Databases intro</t>
+          <t>1.3.1 Compression &amp; encryption; 1.3.2 Databases intro (CAP2/KA4 fb)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.3.1 (RLE encode/decode); begin Quiz 1.3.2; act on CAP2 feedback.</t>
+          <t>Homework 1.3.1; act on CAP2 feedback.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Cumulative 1.1+1.2: Mini-paper 1.2, timed. Programming: Workbook 1 lists &amp; tuples.</t>
+          <t>RECAP CHECKPOINT 1 (1.1-1.2), timed &amp; self-marked; Quiz 1.2.4.</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1.3.2 Databases (normalisation, SQL)</t>
+          <t>1.3.2 Normalisation &amp; SQL (file checks)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Complete Quiz 1.3.2; SQL tasks (Worksheet 1.3); 1NF-3NF practice.</t>
+          <t>Homework 1.3.2 (/20); SQL practice (End-of-Topic Worksheet 1.3 SQL tasks).</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Cover-and-recall KO 1.2. Programming: write SQL in code (Using Databases).</t>
+          <t>Quiz 1.3.1; Revision Notes 1.3.2; file-check prep.</t>
         </is>
       </c>
     </row>
@@ -824,17 +824,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1.3.3 Networks (TCP/IP, LAN/WAN, hardware)</t>
+          <t>1.3.3 Networks, TCP/IP, hardware (RAD day 1)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.3.3 (TCP/IP layer matching); redraw networks diagrams from Diagram bank.</t>
+          <t>Homework 1.3.3 (/20); redraw TCP/IP + topology diagrams (Diagram Bank).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Spaced retrieval 1.1-1.2 (mixed quiz). Programming: Workbook 1 functions + input validation.</t>
+          <t>Quiz 1.3.2; mixed Flashcards 1.1-1.3.</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2.1.4 Thinking logically; 1.3.4 Web tech (HTML/CSS/JS) (CAP2 due)</t>
+          <t>2.1.4 Thinking logically; 1.3.4 HTML/CSS/JS (CAP2 due 7 Dec)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Quiz 2.1.4; Quiz 1.3.4 Sections A-B.</t>
+          <t>Homework 2.1.4 + Homework 1.3.4 Part A.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Retrieval of 1.3.1/1.3.2 (flashcards/quiz A). Programming: Workbook 1 file handling.</t>
+          <t>Quiz 1.3.3; Revision Notes 1.3.4 + 2.1.4.</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1.3.4 Web tech (server/client, indexing, PageRank); EOY quiz</t>
+          <t>1.3.4 Server/client-side, PageRank; EOY quiz (4 days)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Finish Quiz 1.3.4; PageRank explanation; prep EOY quiz with KO 1.1-1.3.</t>
+          <t>Finish Homework 1.3.4; prep EOY quiz with Organisers 1.1-1.3.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Christmas retrieval pack: mixed Flashcards 1.1-1.3 + a Mini-paper. Programming: Workbook 1 OOP.</t>
+          <t>Quiz 1.3.4 + Quiz 2.1.4; Mini-Paper 1.2 timed.</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>One Mini-paper (1.1/1.2/1.3) every few days.</t>
+          <t>RECAP CHECKPOINT 2 (1.1-1.3) over the break, plus one Mini-Paper of choice.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>10 min/day flashcards. Spaced and light.</t>
+          <t>10 min/day flashcards, spaced - nothing heavy.</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1.4.1 Data types (binary, add/subtract, hex)</t>
+          <t>1.4.1 Binary, negatives, add/subtract, hex</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.4.1 Section A + conversion &amp; two's-complement drills (Worksheet 1.4); keep reference sheet.</t>
+          <t>Homework 1.4.1 Part A + conversion drills (End-of-Topic Worksheet 1.4 sA).</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>New-year cumulative 1.1-1.3 (mixed). Programming: Workbook 1 file processing.</t>
+          <t>Mark the holiday Recap 2; re-RAG weak topics on the PLC.</t>
         </is>
       </c>
     </row>
@@ -959,17 +959,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1.4.1 Data types (floating point, bitwise) (KA5)</t>
+          <t>1.4.1 Floating point, bitwise (KA5)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Floating-point normalisation drills (Worksheet 1.4 + topic); revise KA5 with reference sheet.</t>
+          <t>Floating-point drills (Worksheet 1.4 FP activities); prep KA5 with Reference Sheet.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Retrieval of 1.3 (quiz/flashcards); redo slipped binary questions.</t>
+          <t>Quiz 1.4.1 Section A; Revision Notes 1.4.1.</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1.4.1 (char sets); 2.2.1 Programming techniques (KA5 fb; mock week)</t>
+          <t>1.4.1 Character sets; 2.2.1 Constructs (KA5 fb; U6 mocks)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Complete Quiz 1.4.1; Quiz 2.2.1 A-B; act on KA5 feedback.</t>
+          <t>Finish Homework 1.4.1; Homework 2.2.1 Part A; act on KA5 feedback.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Cumulative 1.1-1.3 Mini-paper, timed. Programming: PyGame basics (Component 3).</t>
+          <t>Full Quiz 1.4.1; Flashcards 1.4 started.</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1013,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1.4.2 Data structures (arrays/lists/records/tuples; linked lists; stacks/queues) (CAP3/KA6)</t>
+          <t>1.4.2 Arrays to stacks/queues (CAP3/KA6)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.4.2 (stack/queue trace); revise CAP3/KA6 with KO 1.4.</t>
+          <t>Homework 1.4.2 (/20); prep CAP3/KA6 with Organiser 1.4.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Retrieval 1.4.1 drills + Flashcards 1.2. Programming: Workbook 2 Stack &amp; Queue classes.</t>
+          <t>Quiz 2.2.1; stack/queue traces (Worksheet 1.4 sA); Workbook 2 stack/queue classes.</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Review wk2; 1.4.2 (implement linked lists/stacks/queues - C3)</t>
+          <t>Review wk 2; 1.4.2 implementing (C3) (CAP3/KA6 fb)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Implement linked list/stack/queue in Python (Workbook 2); file-check prep.</t>
+          <t>Implement linked list / stack / queue in Python (Workbook 2); file-check prep.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Retrieval of 1.3: Mini-paper 1.3. Programming: PyGame game states.</t>
+          <t>Quiz 1.4.2 (structures half); Mini-Paper 1.3 timed.</t>
         </is>
       </c>
     </row>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1.4.2 (graphs, trees, hash tables) (CAP3 due)</t>
+          <t>1.4.2 Graphs, trees, hash tables (3 days; CAP3 due 8 Feb)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Remainder of Quiz 1.4.2; implement BST + hash table (Workbook 2).</t>
+          <t>Finish Homework 1.4.2 wrong-answer redos; BST + hash table in Python (Workbook 2).</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Cumulative 1.1-1.4.1 mixed retrieval. Programming: PyGame custom events.</t>
+          <t>Full Quiz 1.4.2; Revision Notes 1.4.2.</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Finish any data-structures implementation.</t>
+          <t>Finish any data-structure implementation.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Flashcards 1.4 + one earlier Mini-paper.</t>
+          <t>Flashcards 1.4 + one earlier Mini-Paper.</t>
         </is>
       </c>
     </row>
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1.4.3 Boolean algebra (logic gates, truth tables) (KA7)</t>
+          <t>1.4.3 Boolean logic, gates, truth tables (KA7)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Quiz 1.4.3 Section A + truth-table completion; revise KA7 with KO 1.4.</t>
+          <t>Homework 1.4.3 Part A; prep KA7.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Retrieval of 1.4.1/1.4.2 (calc + structure traces).</t>
+          <t>Quiz 1.4.3 Section A; truth-table drills (Worksheet 1.4 sA).</t>
         </is>
       </c>
     </row>
@@ -1148,17 +1148,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Component 3 PyGame (sprites, sounds, highscores) (KA7 fb)</t>
+          <t>C3 PyGame sprites/sounds (KA7 fb)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Component 3 PyGame tasks (sprite classes); act on KA7 feedback.</t>
+          <t>PyGame tasks; act on KA7 feedback.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Retrieval: Flashcards 1.4 + a Mini-paper.</t>
+          <t>Full Quiz 1.4.3; Flashcards 1.4.</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1.4.3 Boolean logic (Karnaugh maps, simplifying); Recap 1.2</t>
+          <t>1.4.3 Karnaugh maps, simplification (Recap 1.2 slot)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Boolean simplification / De Morgan's / Karnaugh drills (Worksheet 1.4 + topic); complete Quiz 1.4.3.</t>
+          <t>Finish Homework 1.4.3; K-map + De Morgan drills (Worksheet 1.4 sA).</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Recap 1.2: Mini-paper 1.2 timed + KO 1.2 cover-recall.</t>
+          <t>Mini-Paper 1.2 (SOW Recap-1.2 slot) + Organiser 1.2 cover-recall.</t>
         </is>
       </c>
     </row>
@@ -1202,17 +1202,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CAP4/KA8; 2.1.5 Thinking concurrently; Recap 1.3; Review wk3</t>
+          <t>Review wk 3; CAP4/KA8; 2.1.5 Thinking concurrently (Recap 1.3 slot)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Quiz 2.1.5; revise CAP4/KA8 (cumulative 1.1-1.4 + 2.1).</t>
+          <t>Homework 2.1.5; prep CAP4/KA8 (cumulative 1.1-1.4 + 2.1).</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Recap 1.3: Mini-paper 1.3 + Flashcards 1.3.</t>
+          <t>RECAP CHECKPOINT 3 (1.1-1.4), timed; Mini-Paper 1.3 for the SOW Recap-1.3 slot.</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CAP4/KA8 fb; Component 3 PyGame; Recap 1.4</t>
+          <t>CAP4/KA8 fb; C3 PyGame (Recap 1.4 slot; 4 days; CAP4 due 22 Mar)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Component 3 PyGame workbook; act on CAP4/KA8 feedback.</t>
+          <t>PyGame workbook; act on CAP4/KA8 feedback.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Recap 1.4: Mini-paper 1.4 + reference-sheet number/logic drills.</t>
+          <t>Mini-Paper 1.4 (SOW Recap-1.4 slot) + Reference-Sheet number/logic drills.</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Mock Paper 1 a section at a time, self-marked, RAG-rated.</t>
+          <t>Mock Paper 1 a section at a time, self-marked against its answer sheet.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Top up weak areas with matching subtopic quizzes.</t>
+          <t>Re-RAG the PLC; top up weakest subtopics with their quizzes.</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1283,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Component 3 PyGame; Mock revision</t>
+          <t>C3 PyGame; Mock revision</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sit Mock Paper 1 timed; self-mark; RAG every topic.</t>
+          <t>Sit remaining Mock Paper 1 sections timed; error log.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Target weakest RAG topics with subtopic quizzes/KOs; continue PyGame.</t>
+          <t>Target weakest PLC rows with quizzes/organisers; Exam Technique + Command Words guides.</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Final prep: Mock Paper 1b + error-log review (light).</t>
+          <t>Light: skim Glossary + Common Mistakes; rest.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Skim glossary + common-mistakes sheet; rest before exams.</t>
+          <t>(mock week)</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Component 3 PyGame; mock feedback</t>
+          <t>C3 PyGame; mock feedback (file checks)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>PyGame workbook; act on mock feedback (re-revise weakest).</t>
+          <t>Re-attempt your two weakest mock questions in full.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Re-attempt 2 weakest mock questions; flashcards on those topics.</t>
+          <t>Flashcards on weakest topics; update PLC from mock results.</t>
         </is>
       </c>
     </row>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Mini-NEA: Analysis (CAP5 due 7th)</t>
+          <t>Mini-NEA: Analysis (4 days; CAP5 due 7 May)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Analysis via NEA guide: stakeholder, requirements, measurable success criteria.</t>
+          <t>NEA Template s1 Analysis: stakeholder, requirements, success criteria.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>NEA checklist - criteria testable; 10 min/day flashcards to maintain theory.</t>
+          <t>NEA Guide checklist - every criterion measurable; 10 min/day flashcards.</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Complete analysis write-up (stakeholder research + success criteria).</t>
+          <t>Complete Analysis write-up (research evidence in).</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Peer-review a partner's analysis against the NEA marking checklist.</t>
+          <t>Peer-review a partner's analysis vs the NEA checklist.</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Design: decomposition, algorithms, data structures, UI, test plan (NEA guide).</t>
+          <t>NEA Template s2: decomposition, algorithms, data structures, UI.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Check each design decision links to a requirement.</t>
+          <t>Check each design decision traces to a requirement.</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Complete design + test plan (typical/boundary/erroneous data).</t>
+          <t>Complete s2 + test plan (typical/boundary/erroneous).</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Review design against NEA design checklist.</t>
+          <t>Review vs the Design checklist.</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Finish NEA design so implementation starts cleanly.</t>
+          <t>Finish the design so implementation starts clean.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Light flashcard retrieval to keep theory warm.</t>
+          <t>Light flashcard retrieval.</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Iterative development with annotated evidence + testing each iteration (NEA guide; reuse Workbook 1&amp;2).</t>
+          <t>NEA Template s3: iterative build with annotated evidence + tests per iteration.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Keep a development log; test as you build.</t>
+          <t>Keep the development log as you go.</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Mini-NEA: Implementation; Review wk4</t>
+          <t>Mini-NEA: Implementation (Review wk 4)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Continue implementation; add validation/error handling (robustness).</t>
+          <t>Continue s3; add validation/robustness.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>File-check prep - ensure code evidence is annotated.</t>
+          <t>File-check prep - all code evidence annotated.</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Evaluate against each success criterion with evidence; stakeholder feedback (NEA guide).</t>
+          <t>NEA Template s4: test vs every success criterion, stakeholder feedback.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Map every evaluation point back to an analysis criterion.</t>
+          <t>Map every evaluation point back to Analysis.</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Mini-NEA: Evaluation</t>
+          <t>Mini-NEA: Evaluation (RAD day 3)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Complete evaluation + justified improvements.</t>
+          <t>Complete s4 + justified improvements.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Final NEA checklist; reflect on VESPA targets for Year 13.</t>
+          <t>Final NEA checklist; set VESPA targets for Year 13.</t>
         </is>
       </c>
     </row>
